--- a/MAJSushiConfig/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-family-member-history-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-family-member-history-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -458,7 +458,7 @@
     <t>author</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -563,7 +563,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -612,7 +612,7 @@
     <t>FamilyMemberHistory.extension:author.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -622,7 +622,7 @@
     <t>FamilyMemberHistory.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>FamilyMemberHistory.extension:author.value[x]</t>
@@ -778,7 +778,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1050,7 +1050,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-family-member-history-body-site-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-family-member-history-body-site-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -1066,7 +1066,7 @@
     <t>interpretation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-interpretation-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-interpretation-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -1082,7 +1082,7 @@
     <t>method</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-method-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-method-extension|0.1.0}
 </t>
   </si>
   <si>
